--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/TEXAS_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/TEXAS_2010.xlsx
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C177">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C251">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C285">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C904">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1082">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1083">
@@ -28266,7 +28266,7 @@
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1551">
@@ -28932,7 +28932,7 @@
       </c>
       <c r="B1588" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1588">
@@ -32046,7 +32046,7 @@
       </c>
       <c r="B1761" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1761">
